--- a/sheets/조재수대금교본/검수/바람의 빛깔.xlsx
+++ b/sheets/조재수대금교본/검수/바람의 빛깔.xlsx
@@ -6170,8 +6170,7 @@
       <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-㴌
-‹</t>
+㴌</t>
         </is>
       </c>
       <c r="E6" s="26"/>
@@ -6192,8 +6191,7 @@
       <c r="J6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-汰㴌
-‹</t>
+汰㴌</t>
         </is>
       </c>
       <c r="K6" s="26"/>
@@ -6381,11 +6379,7 @@
         </is>
       </c>
       <c r="M9" s="25"/>
-      <c r="N9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N9" s="21"/>
       <c r="O9" s="25"/>
       <c r="P9" s="21"/>
       <c r="Q9" s="25"/>
@@ -6410,11 +6404,7 @@
         </is>
       </c>
       <c r="E10" s="26"/>
-      <c r="F10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F10" s="21"/>
       <c r="G10" s="26"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
@@ -6564,8 +6554,7 @@
       <c r="N12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-林應
-‹</t>
+林應</t>
         </is>
       </c>
       <c r="O12" s="25"/>
@@ -6593,11 +6582,7 @@
     </row>
     <row r="13" ht="91.25" customHeight="true">
       <c r="A13" s="0"/>
-      <c r="B13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B13" s="21"/>
       <c r="C13" s="25"/>
       <c r="D13" s="21" t="inlineStr">
         <is>
@@ -6707,8 +6692,7 @@
       <c r="N14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-姑
-‹</t>
+姑</t>
         </is>
       </c>
       <c r="O14" s="26"/>
@@ -6866,25 +6850,13 @@
         </is>
       </c>
       <c r="G17" s="25"/>
-      <c r="H17" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H17" s="21"/>
       <c r="I17" s="25"/>
       <c r="J17" s="21"/>
       <c r="K17" s="25"/>
-      <c r="L17" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L17" s="21"/>
       <c r="M17" s="25"/>
-      <c r="N17" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N17" s="21"/>
       <c r="O17" s="25"/>
       <c r="P17" s="21"/>
       <c r="Q17" s="25"/>
@@ -6898,8 +6870,7 @@
       <c r="B18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-南
-‹</t>
+南</t>
         </is>
       </c>
       <c r="C18" s="26"/>
@@ -7075,7 +7046,7 @@
       <c r="S23" s="25"/>
       <c r="T23" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌ㅂ</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="U23" s="25"/>
@@ -7123,11 +7094,7 @@
       <c r="Q25" s="22"/>
       <c r="R25" s="21"/>
       <c r="S25" s="22"/>
-      <c r="T25" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="T25" s="21"/>
       <c r="U25" s="22"/>
     </row>
     <row r="26" ht="91.25" customHeight="true">
@@ -7205,11 +7172,7 @@
       <c r="Q28" s="26"/>
       <c r="R28" s="21"/>
       <c r="S28" s="26"/>
-      <c r="T28" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="T28" s="21"/>
       <c r="U28" s="26"/>
     </row>
     <row r="29" ht="91.25" customHeight="true">
@@ -7287,11 +7250,7 @@
       <c r="Q31" s="25"/>
       <c r="R31" s="21"/>
       <c r="S31" s="25"/>
-      <c r="T31" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="T31" s="21"/>
       <c r="U31" s="25"/>
     </row>
     <row r="32" ht="91.25" customHeight="true">
@@ -7342,11 +7301,7 @@
       <c r="Q33" s="22"/>
       <c r="R33" s="21"/>
       <c r="S33" s="22"/>
-      <c r="T33" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="T33" s="21"/>
       <c r="U33" s="22"/>
     </row>
     <row r="34" ht="91.25" customHeight="true">

--- a/sheets/조재수대금교본/검수/바람의 빛깔.xlsx
+++ b/sheets/조재수대금교본/검수/바람의 빛깔.xlsx
@@ -7046,7 +7046,7 @@
       <c r="S23" s="25"/>
       <c r="T23" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌</t>
+          <t xml:space="preserve">㴌ㅂ</t>
         </is>
       </c>
       <c r="U23" s="25"/>

--- a/sheets/조재수대금교본/검수/바람의 빛깔.xlsx
+++ b/sheets/조재수대금교본/검수/바람의 빛깔.xlsx
@@ -5902,32 +5902,32 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="10.71" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="10.71" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="81.63" customHeight="true">
+    <row r="2" ht="80.0" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -5954,7 +5954,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="91.25" customHeight="true">
+    <row r="3" ht="89.42" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="U3" s="24"/>
     </row>
-    <row r="4" ht="91.25" customHeight="true">
+    <row r="4" ht="89.42" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21"/>
       <c r="C4" s="25"/>
@@ -6092,7 +6092,7 @@
       </c>
       <c r="U4" s="25"/>
     </row>
-    <row r="5" ht="91.25" customHeight="true">
+    <row r="5" ht="89.42" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="U5" s="25"/>
     </row>
-    <row r="6" ht="91.25" customHeight="true">
+    <row r="6" ht="89.42" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -6231,7 +6231,7 @@
       </c>
       <c r="U6" s="26"/>
     </row>
-    <row r="7" ht="91.25" customHeight="true">
+    <row r="7" ht="89.42" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
       </c>
       <c r="U7" s="22"/>
     </row>
-    <row r="8" ht="91.25" customHeight="true">
+    <row r="8" ht="89.42" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -6343,7 +6343,7 @@
       <c r="T8" s="21"/>
       <c r="U8" s="25"/>
     </row>
-    <row r="9" ht="91.25" customHeight="true">
+    <row r="9" ht="89.42" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -6388,7 +6388,7 @@
       <c r="T9" s="21"/>
       <c r="U9" s="25"/>
     </row>
-    <row r="10" ht="91.25" customHeight="true">
+    <row r="10" ht="89.42" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
       </c>
       <c r="U10" s="26"/>
     </row>
-    <row r="11" ht="91.25" customHeight="true">
+    <row r="11" ht="89.42" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -6523,7 +6523,7 @@
       </c>
       <c r="U11" s="22"/>
     </row>
-    <row r="12" ht="91.25" customHeight="true">
+    <row r="12" ht="89.42" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="25"/>
@@ -6580,7 +6580,7 @@
       </c>
       <c r="U12" s="25"/>
     </row>
-    <row r="13" ht="91.25" customHeight="true">
+    <row r="13" ht="89.42" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="25"/>
@@ -6646,7 +6646,7 @@
       </c>
       <c r="U13" s="25"/>
     </row>
-    <row r="14" ht="91.25" customHeight="true">
+    <row r="14" ht="89.42" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -6718,7 +6718,7 @@
       </c>
       <c r="U14" s="26"/>
     </row>
-    <row r="15" ht="91.25" customHeight="true">
+    <row r="15" ht="89.42" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -6785,7 +6785,7 @@
       </c>
       <c r="U15" s="22"/>
     </row>
-    <row r="16" ht="91.25" customHeight="true">
+    <row r="16" ht="89.42" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
       <c r="T16" s="21"/>
       <c r="U16" s="25"/>
     </row>
-    <row r="17" ht="91.25" customHeight="true">
+    <row r="17" ht="89.42" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
       <c r="T17" s="21"/>
       <c r="U17" s="25"/>
     </row>
-    <row r="18" ht="91.25" customHeight="true">
+    <row r="18" ht="89.42" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -6941,7 +6941,7 @@
     <row r="19" ht="6.0" customHeight="true">
       <c r="A19" s="0"/>
     </row>
-    <row r="20" ht="81.63" customHeight="true">
+    <row r="20" ht="80.0" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="20" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
       <c r="T20" s="20"/>
       <c r="U20" s="20"/>
     </row>
-    <row r="21" ht="91.25" customHeight="true">
+    <row r="21" ht="89.42" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21"/>
       <c r="C21" s="22"/>
@@ -6996,7 +6996,7 @@
       </c>
       <c r="U21" s="22"/>
     </row>
-    <row r="22" ht="91.25" customHeight="true">
+    <row r="22" ht="89.42" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21"/>
       <c r="C22" s="25"/>
@@ -7024,7 +7024,7 @@
       </c>
       <c r="U22" s="25"/>
     </row>
-    <row r="23" ht="91.25" customHeight="true">
+    <row r="23" ht="89.42" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="21"/>
       <c r="C23" s="25"/>
@@ -7051,7 +7051,7 @@
       </c>
       <c r="U23" s="25"/>
     </row>
-    <row r="24" ht="91.25" customHeight="true">
+    <row r="24" ht="89.42" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="21"/>
       <c r="C24" s="26"/>
@@ -7074,7 +7074,7 @@
       <c r="T24" s="21"/>
       <c r="U24" s="26"/>
     </row>
-    <row r="25" ht="91.25" customHeight="true">
+    <row r="25" ht="89.42" customHeight="true">
       <c r="A25" s="0"/>
       <c r="B25" s="21"/>
       <c r="C25" s="22"/>
@@ -7097,7 +7097,7 @@
       <c r="T25" s="21"/>
       <c r="U25" s="22"/>
     </row>
-    <row r="26" ht="91.25" customHeight="true">
+    <row r="26" ht="89.42" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="21"/>
       <c r="C26" s="25"/>
@@ -7125,7 +7125,7 @@
       </c>
       <c r="U26" s="25"/>
     </row>
-    <row r="27" ht="91.25" customHeight="true">
+    <row r="27" ht="89.42" customHeight="true">
       <c r="A27" s="0"/>
       <c r="B27" s="21"/>
       <c r="C27" s="25"/>
@@ -7152,7 +7152,7 @@
       </c>
       <c r="U27" s="25"/>
     </row>
-    <row r="28" ht="91.25" customHeight="true">
+    <row r="28" ht="89.42" customHeight="true">
       <c r="A28" s="0"/>
       <c r="B28" s="21"/>
       <c r="C28" s="26"/>
@@ -7175,7 +7175,7 @@
       <c r="T28" s="21"/>
       <c r="U28" s="26"/>
     </row>
-    <row r="29" ht="91.25" customHeight="true">
+    <row r="29" ht="89.42" customHeight="true">
       <c r="A29" s="0"/>
       <c r="B29" s="21"/>
       <c r="C29" s="22"/>
@@ -7203,7 +7203,7 @@
       </c>
       <c r="U29" s="22"/>
     </row>
-    <row r="30" ht="91.25" customHeight="true">
+    <row r="30" ht="89.42" customHeight="true">
       <c r="A30" s="0"/>
       <c r="B30" s="21"/>
       <c r="C30" s="25"/>
@@ -7230,7 +7230,7 @@
       </c>
       <c r="U30" s="25"/>
     </row>
-    <row r="31" ht="91.25" customHeight="true">
+    <row r="31" ht="89.42" customHeight="true">
       <c r="A31" s="0"/>
       <c r="B31" s="21"/>
       <c r="C31" s="25"/>
@@ -7253,7 +7253,7 @@
       <c r="T31" s="21"/>
       <c r="U31" s="25"/>
     </row>
-    <row r="32" ht="91.25" customHeight="true">
+    <row r="32" ht="89.42" customHeight="true">
       <c r="A32" s="0"/>
       <c r="B32" s="21"/>
       <c r="C32" s="26"/>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="U32" s="26"/>
     </row>
-    <row r="33" ht="91.25" customHeight="true">
+    <row r="33" ht="89.42" customHeight="true">
       <c r="A33" s="0"/>
       <c r="B33" s="21"/>
       <c r="C33" s="22"/>
@@ -7304,7 +7304,7 @@
       <c r="T33" s="21"/>
       <c r="U33" s="22"/>
     </row>
-    <row r="34" ht="91.25" customHeight="true">
+    <row r="34" ht="89.42" customHeight="true">
       <c r="A34" s="0"/>
       <c r="B34" s="21"/>
       <c r="C34" s="25"/>
@@ -7331,7 +7331,7 @@
       </c>
       <c r="U34" s="25"/>
     </row>
-    <row r="35" ht="91.25" customHeight="true">
+    <row r="35" ht="89.42" customHeight="true">
       <c r="A35" s="0"/>
       <c r="B35" s="21"/>
       <c r="C35" s="25"/>
@@ -7354,7 +7354,7 @@
       <c r="T35" s="21"/>
       <c r="U35" s="25"/>
     </row>
-    <row r="36" ht="91.25" customHeight="true">
+    <row r="36" ht="89.42" customHeight="true">
       <c r="A36" s="0"/>
       <c r="B36" s="21"/>
       <c r="C36" s="26"/>
@@ -7388,7 +7388,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="49"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="50"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="18" max="16383" man="1"/>
   </rowBreaks>
